--- a/data/flight/titer/Ylipo_BC_LSMMG_1A.xlsx
+++ b/data/flight/titer/Ylipo_BC_LSMMG_1A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ipjos\Downloads\flight 1A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ipjos\code\DARPA_FINAL\data\flight\growth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CABB96D-60AD-4E76-9625-C902362D7349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6D1524-A103-4E25-A7FF-56018717D7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9540" yWindow="3825" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{CEFD99FE-FE29-BA4C-8E21-C28CFAD6EEDC}"/>
+    <workbookView xWindow="3375" yWindow="2640" windowWidth="26385" windowHeight="14250" activeTab="1" xr2:uid="{CEFD99FE-FE29-BA4C-8E21-C28CFAD6EEDC}"/>
   </bookViews>
   <sheets>
     <sheet name="uG growth" sheetId="1" r:id="rId1"/>
@@ -92,7 +92,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -127,6 +127,22 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -145,11 +161,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -176,10 +193,29 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{64A9577C-A047-480D-AB1A-54A8E6148E22}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{9E8B9DF5-AE5F-4E7D-9892-CBFD2A99E41F}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -540,14 +576,14 @@
       <c r="A3" s="8">
         <v>96</v>
       </c>
-      <c r="B3" s="1">
-        <v>1.4549999999999998</v>
+      <c r="B3" s="12">
+        <v>1.03</v>
       </c>
-      <c r="C3" s="1">
-        <v>1.4050000000000002</v>
+      <c r="C3" s="12">
+        <v>1.006</v>
       </c>
-      <c r="D3" s="1">
-        <v>1.49</v>
+      <c r="D3" s="12">
+        <v>1.002</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
@@ -570,14 +606,14 @@
       <c r="A4" s="8">
         <v>96</v>
       </c>
-      <c r="B4" s="1">
-        <v>1.2749999999999999</v>
+      <c r="B4" s="13">
+        <v>0.98699999999999999</v>
       </c>
-      <c r="C4" s="1">
-        <v>1.2250000000000001</v>
+      <c r="C4" s="13">
+        <v>1.0274999999999999</v>
       </c>
-      <c r="D4" s="1">
-        <v>1.34</v>
+      <c r="D4" s="13">
+        <v>0.89450000000000007</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
@@ -600,14 +636,14 @@
       <c r="A5" s="8">
         <v>96</v>
       </c>
-      <c r="B5" s="1">
-        <v>1.4000000000000001</v>
+      <c r="B5" s="12">
+        <v>0.97</v>
       </c>
-      <c r="C5" s="1">
-        <v>1.46</v>
+      <c r="C5" s="12">
+        <v>0.95100000000000007</v>
       </c>
-      <c r="D5" s="1">
-        <v>1.1254999999999999</v>
+      <c r="D5" s="12">
+        <v>0.92149999999999999</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
@@ -630,14 +666,14 @@
       <c r="A6" s="8">
         <v>96</v>
       </c>
-      <c r="B6" s="1">
-        <v>1.395</v>
+      <c r="B6" s="12">
+        <v>0.94450000000000012</v>
       </c>
-      <c r="C6" s="1">
-        <v>1.47</v>
+      <c r="C6" s="12">
+        <v>0.83250000000000002</v>
       </c>
-      <c r="D6" s="1">
-        <v>1.2450000000000001</v>
+      <c r="D6" s="12">
+        <v>0.85699999999999998</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -699,6 +735,9 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
@@ -718,6 +757,9 @@
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
@@ -737,9 +779,9 @@
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
@@ -751,9 +793,9 @@
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -8836,14 +8878,14 @@
       <c r="A3" s="8">
         <v>96</v>
       </c>
-      <c r="B3" s="1">
-        <v>2.5721338453099287</v>
+      <c r="B3" s="14">
+        <v>3.1618211738891939</v>
       </c>
-      <c r="C3" s="1">
-        <v>3.0109709270433354</v>
+      <c r="C3" s="14">
+        <v>3.3812397147558975</v>
       </c>
-      <c r="D3" s="1">
-        <v>3.106966538672518</v>
+      <c r="D3" s="14">
+        <v>2.9972572682391663</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -8852,14 +8894,14 @@
       <c r="A4" s="8">
         <v>96</v>
       </c>
-      <c r="B4" s="1">
-        <v>2.3664289632473947</v>
+      <c r="B4" s="15">
+        <v>3.2441031267142075</v>
       </c>
-      <c r="C4" s="1">
-        <v>2.9149753154141527</v>
+      <c r="C4" s="15">
+        <v>3.1343938562808558</v>
       </c>
-      <c r="D4" s="1">
-        <v>2.0373011519473394</v>
+      <c r="D4" s="15">
+        <v>3.3400987383433902</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -8868,14 +8910,14 @@
       <c r="A5" s="8">
         <v>96</v>
       </c>
-      <c r="B5" s="1">
-        <v>2.6407021393307737</v>
+      <c r="B5" s="14">
+        <v>3.1206801974766871</v>
       </c>
-      <c r="C5" s="1">
-        <v>2.2978606692265497</v>
+      <c r="C5" s="14">
+        <v>3.0658255622600112</v>
       </c>
-      <c r="D5" s="1">
-        <v>2.462424574876577</v>
+      <c r="D5" s="14">
+        <v>2.7229840921557873</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -8884,14 +8926,14 @@
       <c r="A6" s="8">
         <v>96</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="14">
+        <v>2.8464070213933081</v>
+      </c>
+      <c r="C6" s="14">
         <v>2.5584201865057596</v>
       </c>
-      <c r="C6" s="1">
-        <v>2.6955567745474496</v>
-      </c>
-      <c r="D6" s="1">
-        <v>2.6407021393307737</v>
+      <c r="D6" s="14">
+        <v>2.9972572682391663</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
